--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
@@ -2672,11 +2672,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="28460411"/>
-        <c:axId val="34053628"/>
+        <c:axId val="58124598"/>
+        <c:axId val="22277329"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="28460411"/>
+        <c:axId val="58124598"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2710,7 +2710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34053628"/>
+        <c:crossAx val="22277329"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2722,7 +2722,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="34053628"/>
+        <c:axId val="22277329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2765,7 +2765,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28460411"/>
+        <c:crossAx val="58124598"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3504,11 +3504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="12771665"/>
-        <c:axId val="36388041"/>
+        <c:axId val="49126218"/>
+        <c:axId val="36130105"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="12771665"/>
+        <c:axId val="49126218"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3540,14 +3540,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36388041"/>
+        <c:crossAx val="36130105"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="36388041"/>
+        <c:axId val="36130105"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3621,7 +3621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12771665"/>
+        <c:crossAx val="49126218"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7851,7 +7851,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -8403,23 +8403,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -12315,7 +12315,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17864,15 +17864,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>86.2114148401699</v>
+        <v>87.4474203710322</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -17971,23 +17971,23 @@
       </c>
       <c r="T2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="H39" s="96" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="96"/>
       <c r="J39" s="96"/>
@@ -19089,7 +19089,7 @@
       <c r="P39" s="96"/>
       <c r="Q39" s="96" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
@@ -2672,11 +2672,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58124598"/>
-        <c:axId val="22277329"/>
+        <c:axId val="42770759"/>
+        <c:axId val="54766618"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="58124598"/>
+        <c:axId val="42770759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2710,7 +2710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22277329"/>
+        <c:crossAx val="54766618"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2722,7 +2722,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="22277329"/>
+        <c:axId val="54766618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2765,7 +2765,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58124598"/>
+        <c:crossAx val="42770759"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3504,11 +3504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="49126218"/>
-        <c:axId val="36130105"/>
+        <c:axId val="37677129"/>
+        <c:axId val="17293248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="49126218"/>
+        <c:axId val="37677129"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3540,14 +3540,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36130105"/>
+        <c:crossAx val="17293248"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="36130105"/>
+        <c:axId val="17293248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3621,7 +3621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49126218"/>
+        <c:crossAx val="37677129"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
@@ -2672,11 +2672,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42770759"/>
-        <c:axId val="54766618"/>
+        <c:axId val="60509526"/>
+        <c:axId val="62861824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="42770759"/>
+        <c:axId val="60509526"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2710,7 +2710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54766618"/>
+        <c:crossAx val="62861824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2722,7 +2722,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="54766618"/>
+        <c:axId val="62861824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2765,7 +2765,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42770759"/>
+        <c:crossAx val="60509526"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3504,11 +3504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="37677129"/>
-        <c:axId val="17293248"/>
+        <c:axId val="37509511"/>
+        <c:axId val="72348735"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="37677129"/>
+        <c:axId val="37509511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3540,14 +3540,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17293248"/>
+        <c:crossAx val="72348735"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="17293248"/>
+        <c:axId val="72348735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3621,7 +3621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37677129"/>
+        <c:crossAx val="37509511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Monetario_I.xlsx
@@ -2672,11 +2672,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60509526"/>
-        <c:axId val="62861824"/>
+        <c:axId val="57045160"/>
+        <c:axId val="59909125"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="60509526"/>
+        <c:axId val="57045160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2710,7 +2710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62861824"/>
+        <c:crossAx val="59909125"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2722,7 +2722,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="62861824"/>
+        <c:axId val="59909125"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2765,7 +2765,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60509526"/>
+        <c:crossAx val="57045160"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3504,11 +3504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="37509511"/>
-        <c:axId val="72348735"/>
+        <c:axId val="16878410"/>
+        <c:axId val="3751323"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="37509511"/>
+        <c:axId val="16878410"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3540,14 +3540,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72348735"/>
+        <c:crossAx val="3751323"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="72348735"/>
+        <c:axId val="3751323"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3621,7 +3621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37509511"/>
+        <c:crossAx val="16878410"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
